--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_383_R40.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_383_R40.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6055</v>
+        <v>5.0252</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4333</v>
+        <v>3.3378</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1722</v>
+        <v>1.6874</v>
       </c>
       <c r="G2" t="n">
         <v>3.7203</v>
@@ -610,13 +610,13 @@
         <v>1.8198</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2028</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2573</v>
+        <v>0.1618</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9455</v>
+        <v>0.4607</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0814</v>
+        <v>2.1708</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0115</v>
+        <v>0.4777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0699</v>
+        <v>1.6931</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2127</v>
+        <v>4.6284</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6383</v>
+        <v>0.8608</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4256</v>
+        <v>3.7677</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9641</v>
+        <v>5.7666</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3285</v>
+        <v>2.4098</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3644</v>
+        <v>3.3568</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7513</v>
+        <v>-1.1382</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6901</v>
+        <v>-1.549</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0612</v>
+        <v>0.4108</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6824</v>
+        <v>-1.8198</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-4.5495</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6824</v>
+        <v>2.7297</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1862</v>
+        <v>-0.7962</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0474</v>
+        <v>-0.8978</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1388</v>
+        <v>0.1016</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8424</v>
+        <v>1.8973</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5624</v>
+        <v>1.3455</v>
       </c>
       <c r="F4" t="n">
-        <v>0.28</v>
+        <v>0.5517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6001</v>
+        <v>1.5973</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5355</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9354</v>
+        <v>2.5837</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7652</v>
+        <v>2.7455</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3944</v>
+        <v>0.1669</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6292</v>
+        <v>2.5786</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1651</v>
+        <v>-1.1482</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8589</v>
+        <v>-1.1533</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3062</v>
+        <v>0.0051</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9099</v>
+        <v>-0.4549</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1374</v>
+        <v>-2.2747</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0473</v>
+        <v>1.8198</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4908</v>
+        <v>-0.3352</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1555</v>
+        <v>-0.2153</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6463</v>
+        <v>-0.1199</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1583</v>
+        <v>1.0901</v>
       </c>
       <c r="W4" t="n">
         <v>1.0901</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4704</v>
+        <v>1.5836</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0611</v>
+        <v>1.6106</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5315</v>
+        <v>-0.027</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6284</v>
+        <v>0.2127</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8608</v>
+        <v>0.6383</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7677</v>
+        <v>-0.4256</v>
       </c>
       <c r="J5" t="n">
-        <v>5.7666</v>
+        <v>0.9641</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4098</v>
+        <v>1.3285</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3568</v>
+        <v>-0.3644</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1382</v>
+        <v>-0.7513</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.549</v>
+        <v>-0.6901</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4108</v>
+        <v>-0.0612</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8198</v>
+        <v>0.6824</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.5495</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7297</v>
+        <v>0.6824</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4966</v>
+        <v>0.6885</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4365</v>
+        <v>0.6466</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06</v>
+        <v>0.0419</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.028</v>
+        <v>1.2857</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4117</v>
+        <v>1.3289</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6163999999999999</v>
+        <v>-0.0432</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5973</v>
+        <v>0.6001</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9864000000000001</v>
+        <v>1.5355</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5837</v>
+        <v>-0.9354</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7455</v>
+        <v>1.7652</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1669</v>
+        <v>2.3944</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5786</v>
+        <v>-0.6292</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1482</v>
+        <v>-1.1651</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1533</v>
+        <v>-0.8589</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0051</v>
+        <v>-0.3062</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4549</v>
+        <v>0.9099</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2747</v>
+        <v>-1.1374</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8198</v>
+        <v>2.0473</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2045</v>
+        <v>-0.0659</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1492</v>
+        <v>-0.389</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0552</v>
+        <v>0.3231</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0901</v>
+        <v>-0.1583</v>
       </c>
       <c r="W6" t="n">
         <v>1.0901</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2485</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1079</v>
+        <v>0.2138</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9169</v>
+        <v>-2.1447</v>
       </c>
       <c r="F7" t="n">
-        <v>1.809</v>
+        <v>2.3585</v>
       </c>
       <c r="G7" t="n">
         <v>0.3809</v>
@@ -1000,13 +1000,13 @@
         <v>1.3648</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.669</v>
+        <v>-0.3472</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1492</v>
+        <v>-0.377</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5197000000000001</v>
+        <v>0.0297</v>
       </c>
       <c r="V7" t="n">
         <v>1.0901</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1104</v>
+        <v>-0.015</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3503</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2399</v>
+        <v>0.5631</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3508</v>
@@ -1078,13 +1078,13 @@
         <v>0.9099</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3528</v>
+        <v>-0.2574</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7901</v>
+        <v>-0.0178</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5628</v>
+        <v>-0.2395</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3167</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2478</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9195</v>
+        <v>-1.4526</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6717</v>
+        <v>0.704</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4968</v>
@@ -1156,13 +1156,13 @@
         <v>1.1374</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8883</v>
+        <v>-0.3891</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6464</v>
+        <v>-0.1795</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2419</v>
+        <v>-0.2096</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4707</v>
+        <v>-1.9628</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9403</v>
+        <v>-3.3354</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4696</v>
+        <v>1.3726</v>
       </c>
       <c r="G10" t="n">
         <v>-4.2322</v>
@@ -1234,13 +1234,13 @@
         <v>2.2747</v>
       </c>
       <c r="S10" t="n">
-        <v>0.534</v>
+        <v>0.0419</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4073</v>
+        <v>0.0121</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1267</v>
+        <v>0.0297</v>
       </c>
       <c r="V10" t="n">
         <v>1.0901</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.090900000000001</v>
+        <v>9.450100000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.230799999999999</v>
+        <v>0.5897000000000006</v>
       </c>
       <c r="F11" t="n">
-        <v>8.860200000000001</v>
+        <v>8.860199999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>5.0599</v>
+        <v>5.059900000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08449999999999913</v>
+        <v>0.0844999999999998</v>
       </c>
       <c r="I11" t="n">
         <v>4.9756</v>
@@ -1288,7 +1288,7 @@
         <v>9.838100000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>8.167000000000002</v>
+        <v>8.167</v>
       </c>
       <c r="L11" t="n">
         <v>1.671</v>
@@ -1312,13 +1312,13 @@
         <v>14.7858</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1974</v>
+        <v>-0.8381000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6149</v>
+        <v>-1.2559</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4177000000000002</v>
+        <v>0.4177</v>
       </c>
       <c r="V11" t="n">
         <v>2.9536</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.0109</v>
+        <v>1.7504</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5429</v>
+        <v>-0.0408</v>
       </c>
       <c r="F12" t="n">
-        <v>1.468</v>
+        <v>1.7912</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6597</v>
@@ -1390,13 +1390,13 @@
         <v>2.0473</v>
       </c>
       <c r="S12" t="n">
-        <v>0.898</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5629</v>
+        <v>-0.0208</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3351</v>
+        <v>0.6584</v>
       </c>
       <c r="V12" t="n">
         <v>1.0901</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5648</v>
+        <v>0.8225</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3217</v>
+        <v>1.158</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2431</v>
+        <v>-0.3355</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0575</v>
+        <v>-0.3215</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5145999999999999</v>
+        <v>-0.2603</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.0612</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2526</v>
+        <v>-0.2434</v>
       </c>
       <c r="K13" t="n">
-        <v>2.358</v>
+        <v>-0.2434</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1054</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3101</v>
+        <v>-0.0781</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8434</v>
+        <v>-0.0169</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5333</v>
+        <v>-0.0612</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6824</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3648</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0473</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3266</v>
+        <v>0.0539</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2756</v>
+        <v>0.3113</v>
       </c>
       <c r="U13" t="n">
-        <v>1.051</v>
+        <v>-0.2574</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3867</v>
+        <v>1.0901</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1583</v>
+        <v>1.0901</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2571</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6249</v>
+        <v>-0.1452</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3679</v>
+        <v>0.9522</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3215</v>
+        <v>-0.0575</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2603</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0612</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2434</v>
+        <v>1.2526</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2434</v>
+        <v>2.358</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-1.1054</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0781</v>
+        <v>-1.3101</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0169</v>
+        <v>-1.8434</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0612</v>
+        <v>0.5333</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.6824</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.3648</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.0473</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4885</v>
+        <v>0.5687</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7782</v>
+        <v>-0.1913</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2897</v>
+        <v>0.7601</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0901</v>
+        <v>-0.3867</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0901</v>
+        <v>0.1583</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5451</v>
       </c>
     </row>
     <row r="15">
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0295</v>
+        <v>0.796</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2573</v>
+        <v>-0.4908</v>
       </c>
       <c r="F15" t="n">
         <v>1.2868</v>
@@ -1624,10 +1624,10 @@
         <v>1.1374</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8501</v>
+        <v>0.6166</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2156</v>
+        <v>-0.0178</v>
       </c>
       <c r="U15" t="n">
         <v>0.6344</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4692</v>
+        <v>0.0239</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0077</v>
+        <v>-0.6196</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4769</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.989</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.8292</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3312</v>
+        <v>-0.9191</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7747</v>
+        <v>0.757</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1042</v>
+        <v>0.9643</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6705</v>
+        <v>-0.2072</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7857</v>
+        <v>-0.8469</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4463</v>
+        <v>-0.135</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3393</v>
+        <v>-0.7119</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8198</v>
+        <v>0.2275</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2747</v>
+        <v>-1.1374</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4549</v>
+        <v>1.3648</v>
       </c>
       <c r="S16" t="n">
-        <v>1.135</v>
+        <v>-0.1137</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2812</v>
+        <v>-0.2393</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1462</v>
+        <v>0.1256</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7734</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7734</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7986</v>
+        <v>-1.084</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0866</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.288</v>
+        <v>-0.5069</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-1.4102</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8292</v>
+        <v>-0.6545</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9191</v>
+        <v>-0.7558</v>
       </c>
       <c r="J17" t="n">
-        <v>0.757</v>
+        <v>-0.5802</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9643</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2072</v>
+        <v>0.1118</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8469</v>
+        <v>-0.83</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.135</v>
+        <v>0.0375</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7119</v>
+        <v>-0.8675</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2275</v>
+        <v>0.4549</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3648</v>
+        <v>0.4549</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9362</v>
+        <v>-0.1287</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7063</v>
+        <v>0.0031</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2299</v>
+        <v>-0.1318</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1757</v>
+        <v>-1.2302</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9274</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2483</v>
+        <v>-0.5967</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4102</v>
+        <v>-0.6166</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6545</v>
+        <v>0.6061</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7558</v>
+        <v>-1.2227</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5802</v>
+        <v>0.2134</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6919999999999999</v>
+        <v>0.8799</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1118</v>
+        <v>-0.6665</v>
       </c>
       <c r="M18" t="n">
         <v>-0.83</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0375</v>
+        <v>-0.2738</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8675</v>
+        <v>-0.5562</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4549</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R18" t="n">
         <v>0.4549</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2204</v>
+        <v>0.0688</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3471</v>
+        <v>0.2904</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1268</v>
+        <v>-0.2216</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4835</v>
+        <v>-1.3179</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9838</v>
+        <v>-0.8743</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4997</v>
+        <v>-0.4436</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6166</v>
+        <v>-0.9438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6061</v>
+        <v>-1.3296</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2227</v>
+        <v>0.3858</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2134</v>
+        <v>-0.7037</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8799</v>
+        <v>-0.7782</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6665</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.83</v>
+        <v>-0.24</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2738</v>
+        <v>-0.5513</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5562</v>
+        <v>0.3113</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6824</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4549</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1844</v>
+        <v>-0.3741</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0598</v>
+        <v>-0.1706</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1246</v>
+        <v>-0.2036</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4993</v>
+        <v>-1.4156</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.991</v>
+        <v>-0.8094</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5082</v>
+        <v>-0.6062</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9438</v>
+        <v>0.989</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3296</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3858</v>
+        <v>0.3312</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7037</v>
+        <v>1.7747</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7782</v>
+        <v>1.1042</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0745</v>
+        <v>0.6705</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.24</v>
+        <v>-0.7857</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5513</v>
+        <v>-0.4463</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3113</v>
+        <v>-0.3393</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.8198</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.4549</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5555</v>
+        <v>0.1886</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2873</v>
+        <v>0.464</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2682</v>
+        <v>-0.2755</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.7734</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.7734</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5684</v>
+        <v>-1.6581</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0463</v>
+        <v>-0.8128</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.522</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>3.2219</v>
@@ -2092,13 +2092,13 @@
         <v>2.0473</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1197</v>
+        <v>0.0299</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6463</v>
+        <v>-0.4128</v>
       </c>
       <c r="U21" t="n">
-        <v>0.766</v>
+        <v>0.4427</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1802</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5913</v>
+        <v>-3.1118</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0847</v>
+        <v>-1.7345</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5066</v>
+        <v>-1.3773</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3367</v>
@@ -2170,13 +2170,13 @@
         <v>0.4549</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5722</v>
+        <v>-0.0927</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3471</v>
+        <v>0.0031</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2251</v>
+        <v>-0.0958</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3674</v>
+        <v>-3.4731</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9804</v>
+        <v>-3.28</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.387</v>
+        <v>-0.1931</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6497</v>
@@ -2248,13 +2248,13 @@
         <v>2.0473</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1517</v>
+        <v>-0.2574</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1372</v>
+        <v>-0.4368</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0145</v>
+        <v>0.1794</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2485</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.091100000000001</v>
+        <v>-9.0909</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.860300000000001</v>
+        <v>-8.860099999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2307000000000001</v>
+        <v>-0.2308000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-5.0601</v>
@@ -2329,10 +2329,10 @@
         <v>1.1975</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4176000000000004</v>
+        <v>-0.4175</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6151</v>
+        <v>1.6149</v>
       </c>
       <c r="V24" t="n">
         <v>-2.9537</v>
